--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/GEORGIA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/GEORGIA_2011.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C174">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C205">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C740">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C839">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C878">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C879">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C886">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1260">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1286">
@@ -26250,7 +26250,7 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1439">
